--- a/public/exports-from-60-with-coowners/66137112.xlsx
+++ b/public/exports-from-60-with-coowners/66137112.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311148948</t>
+          <t xml:space="preserve">311148949</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">

--- a/public/exports-from-60-with-coowners/66137112.xlsx
+++ b/public/exports-from-60-with-coowners/66137112.xlsx
@@ -4639,7 +4639,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311148949</t>
+          <t xml:space="preserve">311148948</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
